--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>121701352</v>
       </c>
       <c r="B2" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>121701352</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>121701352</v>
       </c>
       <c r="B2" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -709,16 +709,8 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>121701352</v>
       </c>
       <c r="B2" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>121701352</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>121701352</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>121701352</v>
       </c>
       <c r="B2" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
